--- a/Single_word.xlsx
+++ b/Single_word.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="633">
   <si>
     <t>cat</t>
   </si>
@@ -2112,6 +2112,941 @@
   </si>
   <si>
     <t>法律 +名词后缀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cold</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嫦娥变老了之后非常怕冷，很容易感冒。</t>
+  </si>
+  <si>
+    <t>adj. 冷的；寒冷的；n. 低气温；感冒</t>
+  </si>
+  <si>
+    <t>clear</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嫦娥拿着一根棍子清理猪耳朵。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 清理；（使）变清醒；adj. 清楚的</t>
+  </si>
+  <si>
+    <t>clean</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v./n 打扫；v. 使…干净；adj. 整洁的；干净的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>清理门口的垃圾，环境就会变得干净，整洁。</t>
+  </si>
+  <si>
+    <t>class</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 上课；课；班级；种类；vt. 把…归入某等级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嫦娥拉着两条蛇去班级上课。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>lassmate</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 同学；同班同学</t>
+  </si>
+  <si>
+    <t>班级+伙伴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clever</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 聪明的；熟练的；灵巧的</t>
+  </si>
+  <si>
+    <t>嫦娥喝了可乐，吃了维生素E后，连小草都觉得她变聪明了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cloud</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 云朵；阴；忧郁；v. 使模糊</t>
+  </si>
+  <si>
+    <t>嫦娥在楼梯上和弟弟一起观察云朵。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cloudy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 多云的；阴云密布的；阴天的</t>
+  </si>
+  <si>
+    <t>云朵的形容词</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cross</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 十字路口；人行横道；交叉点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嫦娥用肉奖励穿越马路的两条蛇。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rossing</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 穿越；渡过；相交；n. 十字架</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cross</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prep. 穿过；prep./adv. 从…一边到另一边；横过；在…对面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>穿过人行横道。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在 + 穿越</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hicken</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 鸡；鸡肉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吃饭的嫦娥在啃一只鸡。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ook</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 烹调；烹饪；n. 厨师；炊事员</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嫦娥用望远镜看厨师烹饪做菜。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ooking</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t> ing名词后缀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 烹饪；烹调；食物；adj. 适于烹饪的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>all</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v./n. 打电话；v. 呼叫；称呼；把…叫做；n. 通话；叫声</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嫦娥所有的时间都在打电话。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hange</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v./n. 变化；改变；替代；v. 兑换；n. 变更；变革</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嫦娥奔月后发生了很大变化。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>limb</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v./n. 攀登；v. 爬；登山；爬升；晋升；n. 增值；增加</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嫦娥带着梨和抹布爬山。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>l</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ose</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 失去；丢失；遗失</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小威10只彩色的笔丢失了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>l</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>oss</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 丧失；损失；丢失</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10条五步蛇丢失了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>close</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 关；关闭；不开放；停业；（使）结束；n. 结束；adj. 亲密的；密切的；adv. 靠近；紧挨着</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嫦娥丢失了很多货物，于是关闭商店，停业，结束了自己的事业。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>l</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ock</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v./n. 锁；v. 被锁住；把…锁起来；n. 车锁；制动器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10个刺客被锁了起来。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>lock</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嫦娥用锁把钟锁起来。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 时钟；钟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>o</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ver</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adv. 结束；穿过；翻转；以上；prep. 在…上面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸡蛋把维生素E放在草地上面之后，结束了一天的工作。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>over</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 盖；覆盖；掩蔽；撒上；n. 罩子；覆盖物；躲避处；封面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嫦娥在头上面盖了个罩子。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>p</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ublic</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 公共的，公立的；公众的，大众的；n. 公众，大众</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>瀑布旁，厉害的嫦娥变成了公共的神，为大众做了很多好事，还成了公立的各种机构。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>low</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 慢的；迟缓的；低速的；迟钝的；adv. 缓慢地；v. （使）放慢速度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白娘子拖着着10个皇冠走得很慢。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ay</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vt. 说，讲；宣称，说明；n. 发言权，决定权；int. （吃惊或吸引注意力）哎呀，喂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白娘子跟阿姨说话。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 座位；（椅子等的）座部；（机器的）基座；v. 使坐下，使就座</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>eat</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白娘子坐在座位上吃饭。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>it</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 坐；坐下，就座；n. 坐的一段时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小威在四把伞下坐着。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>now</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 雪；雪花；v. 下雪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白娘子不带女王去看雪。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nowy</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 下雪的；雪白的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雪的形容词</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>snowman</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雪人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雪 + 男人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 巴士；公共汽车</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布被白娘子搬上巴士。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nake</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白娘子在那棵树上变成了蛇。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 蛇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pace</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白娘子趴在一个空间很大，很宽敞的厕所里面。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 空间；宽敞；空旷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>chool</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. （中、小）学校；上学；学院；vt. 教育</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白娘子超越同学，第1名到达学校。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>schoolbag</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>背去学校的包是书包。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 书包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>smoke</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 烟，烟雾；v. 吸烟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白娘子摸科学家，科学家吓得冒烟了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>sp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>end</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 度过，花（时间）；n. 花费，开销；预算</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白娘子的钢笔是弟弟花费了大价钱买的。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 运动；体育运动；v. 嬉戏；adj. 运动的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白娘子在坡上边吃软糖边做运动。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sport</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 状态，状况；国家；adj. 州的；国事的；v. 陈述，说明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白娘子跟塔里的特警陈述国家目前的状况。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tate</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 车站；电视台</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>国家建立了很多车站。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tation</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>p</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ass</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v./n. 通过；及格；v. 走过；传球；转移给；大于；n. 通行证；车票；关口；阶段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>怕死的白娘子走过一段独木桥之后，通过了测验，及格了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 声音；响声；音响；嗓音；v. 听起来好像；鸣警报；adj. 明智的；合理的；正确的；adv. 酣（睡）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白娘子从圆形的小孔里听到声音。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 错过；未击中；未得到；不懂；思念；；n. 小姐，女士</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>迷失的白娘子错过末班车，很思念家，于是找了位小姐寻求帮助。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ound</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>m</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>iss</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2666,12 +3601,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D165"/>
+  <dimension ref="A1:D210"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="9.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="73.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="86.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="79.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="97.375" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
@@ -4499,6 +5434,501 @@
         <v>494</v>
       </c>
     </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A166" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A167" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A168" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A169" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A170" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A171" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A172" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A173" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A174" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A175" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A176" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A177" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A178" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A179" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A180" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A181" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A182" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A183" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A184" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A185" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A186" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A187" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A188" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A189" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A190" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A191" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A192" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A193" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A194" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A195" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A196" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A197" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A198" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A199" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A200" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A201" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A202" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A203" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A204" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A205" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A206" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A207" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A208" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A209" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A210" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>629</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Single_word.xlsx
+++ b/Single_word.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24060" windowHeight="3360"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="1033">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1200" uniqueCount="1198">
   <si>
     <t>English</t>
   </si>
@@ -2238,6 +2238,9 @@
     <t>n. 鸭子；鸭肉</t>
   </si>
   <si>
+    <t>check</t>
+  </si>
+  <si>
     <t>车被刺客检查了个遍</t>
   </si>
   <si>
@@ -2775,6 +2778,9 @@
     <t>n. 太阳；阳光；恒星；vt. 晒太阳</t>
   </si>
   <si>
+    <t>spring</t>
+  </si>
+  <si>
     <t>小威用水瓶里的水给草浇水，因为现在是春天。</t>
   </si>
   <si>
@@ -3081,7 +3087,7 @@
     <t>story</t>
   </si>
   <si>
-    <t>小威在石头上用乳液写了个小故事。</t>
+    <t>小威在石头上用o牌乳液写了个小故事。</t>
   </si>
   <si>
     <t>n. 故事；小说；情节；vi. 讲…的故事</t>
@@ -3114,11 +3120,499 @@
     <t>v. 展示；显示，表明；出示；n. 演出，歌舞表演</t>
   </si>
   <si>
-    <t>check</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>spring</t>
+    <t>lead</t>
+  </si>
+  <si>
+    <t>小威把可乐和阿迪鞋给了领路的人。</t>
+  </si>
+  <si>
+    <t>v. 领路；领导；通向；导致；n. 领先地位；实例；榜样；线索</t>
+  </si>
+  <si>
+    <t>leader</t>
+  </si>
+  <si>
+    <t>lead名词</t>
+  </si>
+  <si>
+    <t>n. 领导；领袖；最佳的人（或物）</t>
+  </si>
+  <si>
+    <t>full</t>
+  </si>
+  <si>
+    <t>扶着墙，拿着筷子的小威说，我吃得太饱了，吃不下了。</t>
+  </si>
+  <si>
+    <t>adj. 满的；饱的；丰富的；完全的；n. 完全</t>
+  </si>
+  <si>
+    <t>road</t>
+  </si>
+  <si>
+    <t>小威吃了肉穿好阿迪鞋子在路上奔跑。</t>
+  </si>
+  <si>
+    <t>n. 路；道路；途径；方法</t>
+  </si>
+  <si>
+    <t>mouth</t>
+  </si>
+  <si>
+    <t>小威在麦当劳前把藕和桃花塞在嘴里。</t>
+  </si>
+  <si>
+    <t>n. 嘴；口；入口；开口</t>
+  </si>
+  <si>
+    <t>nose</t>
+  </si>
+  <si>
+    <t>不要用彩色的笔涂鼻子。</t>
+  </si>
+  <si>
+    <t>n. 鼻子；嗅觉；v. （用鼻子）嗅，拱，顶</t>
+  </si>
+  <si>
+    <t>hair</t>
+  </si>
+  <si>
+    <t>小威坐在椅子上，头发被吹到空气中。</t>
+  </si>
+  <si>
+    <t>n. （尤指）头发；毛发；（植物叶茎上的）茸毛</t>
+  </si>
+  <si>
+    <t>cough</t>
+  </si>
+  <si>
+    <t>小威凑近桂花就会咳嗽。</t>
+  </si>
+  <si>
+    <t>v./n. 咳嗽；咳出；n. 咳嗽声</t>
+  </si>
+  <si>
+    <t>guide</t>
+  </si>
+  <si>
+    <t>小威雇了一个很贵的导游。</t>
+  </si>
+  <si>
+    <t>vt. 指导；给某人领路；解释；n. 指南；导游；手册</t>
+  </si>
+  <si>
+    <t>ice</t>
+  </si>
+  <si>
+    <t>小威非常爱在厕所前吃冰淇淋。</t>
+  </si>
+  <si>
+    <t>n. 冰；冰块；v. （使）结冰；冰镇；adj. 冰的；冰制的</t>
+  </si>
+  <si>
+    <t>choice</t>
+  </si>
+  <si>
+    <t>臭的冰块是小威唯一的选择。</t>
+  </si>
+  <si>
+    <t>n. 选择；选择权</t>
+  </si>
+  <si>
+    <t>lamp</t>
+  </si>
+  <si>
+    <t>小威把辣椒和地图放在台灯下。</t>
+  </si>
+  <si>
+    <t>n. 灯；发热灯；v. 〈诗〉照亮；看到</t>
+  </si>
+  <si>
+    <t>dollar</t>
+  </si>
+  <si>
+    <t>小威用兜里的筷子和矮人换了一美元。</t>
+  </si>
+  <si>
+    <t>n. 美元；一元</t>
+  </si>
+  <si>
+    <t>tire</t>
+  </si>
+  <si>
+    <t>小威身体很热，感觉很疲倦，但是还得继续修轮胎。</t>
+  </si>
+  <si>
+    <t>v. （使）疲劳，疲倦，困倦；n. 轮胎</t>
+  </si>
+  <si>
+    <t>tired</t>
+  </si>
+  <si>
+    <t>tire形容词后缀</t>
+  </si>
+  <si>
+    <t>adj. 疲倦的；厌倦的；厌烦的；疲劳的</t>
+  </si>
+  <si>
+    <t>letter</t>
+  </si>
+  <si>
+    <t>小威喝着可乐，偷偷给耳康写信，但是只写了几个字母。</t>
+  </si>
+  <si>
+    <t>n. 信；函；字母；v. 用字母标明</t>
+  </si>
+  <si>
+    <t>Italian</t>
+  </si>
+  <si>
+    <t>小威把一朵宝塔前的莲花送给了意大利人。</t>
+  </si>
+  <si>
+    <t>n. 意大利人；意大利语；adj. 意大利的；意大利语的；意大利人的</t>
+  </si>
+  <si>
+    <t>drawer</t>
+  </si>
+  <si>
+    <t>小威把画好的耳朵图片放进抽屉。</t>
+  </si>
+  <si>
+    <t>n. 抽屉；开票人；出票人</t>
+  </si>
+  <si>
+    <t>way</t>
+  </si>
+  <si>
+    <t>青蛙用尽非常多方法和手段，把树丫种在道路旁。</t>
+  </si>
+  <si>
+    <t>n. 方法；手段；道路；adv. 很远；大量；非常</t>
+  </si>
+  <si>
+    <t>away</t>
+  </si>
+  <si>
+    <t>小威一个人在道路上朝另一个方向走去，离开了家，去了别处。</t>
+  </si>
+  <si>
+    <t>adv. 离开；去别处；朝另一个方向；不在</t>
+  </si>
+  <si>
+    <t>bell</t>
+  </si>
+  <si>
+    <t>小威在被子里给筷子系铃铛。</t>
+  </si>
+  <si>
+    <t>n. 钟（声）；铃（声）；vi. 系铃于；鸣钟</t>
+  </si>
+  <si>
+    <t>case</t>
+  </si>
+  <si>
+    <t>小威擦了擦用彩色笔标记的那个案例</t>
+  </si>
+  <si>
+    <t>n. 案例；实例；具体情况；事实；论据；病例；vt. 围绕；包盖</t>
+  </si>
+  <si>
+    <t>parent</t>
+  </si>
+  <si>
+    <t>小威趴在地上认同父母亲说的话。</t>
+  </si>
+  <si>
+    <t>n. 父母亲；父本，母本；创始机构</t>
+  </si>
+  <si>
+    <t>park</t>
+  </si>
+  <si>
+    <t>小威很怕在人口很多的公园停车。</t>
+  </si>
+  <si>
+    <t>n. 公园；专用区；园区；庄园；v. 停（车）；坐下；把…搁置</t>
+  </si>
+  <si>
+    <t>tea</t>
+  </si>
+  <si>
+    <t>特警在喝苹果味的水果茶。</t>
+  </si>
+  <si>
+    <t>n. 茶叶；茶；茶水</t>
+  </si>
+  <si>
+    <t>teach</t>
+  </si>
+  <si>
+    <t>把茶包放进茶壶后，老师开始教课。</t>
+  </si>
+  <si>
+    <t>v. 教（课程）；讲授；训练；教育</t>
+  </si>
+  <si>
+    <t>teacher</t>
+  </si>
+  <si>
+    <t>n. 教师；教员；老师</t>
+  </si>
+  <si>
+    <t>cute</t>
+  </si>
+  <si>
+    <t>喝醋的特警特别可爱。</t>
+  </si>
+  <si>
+    <t>adj. 可爱的；漂亮迷人的</t>
+  </si>
+  <si>
+    <t>tell</t>
+  </si>
+  <si>
+    <t>特警拄着拐杖说话。</t>
+  </si>
+  <si>
+    <t>v. 说；告诉；说明；讲述；n. 谈话；传闻</t>
+  </si>
+  <si>
+    <t>quiet</t>
+  </si>
+  <si>
+    <t>蛐蛐点着蜡烛，让ET外星人保持安静。</t>
+  </si>
+  <si>
+    <t>adj. 安静的；轻声的；轻柔的；n. 安静；宁静；v. （使）平静</t>
+  </si>
+  <si>
+    <t>quite</t>
+  </si>
+  <si>
+    <t>蛐蛐把蜡烛送给他非常喜欢的特警。</t>
+  </si>
+  <si>
+    <t>adv. 非常；相当地；很；十分；完全</t>
+  </si>
+  <si>
+    <t>police</t>
+  </si>
+  <si>
+    <t>在坡上拿着梨站在厕所前的是警察。</t>
+  </si>
+  <si>
+    <t>n. 警察；警察部门</t>
+  </si>
+  <si>
+    <t>policeman</t>
+  </si>
+  <si>
+    <t>警察 + 男人</t>
+  </si>
+  <si>
+    <t>n. 警察；男警察</t>
+  </si>
+  <si>
+    <t>policewoman</t>
+  </si>
+  <si>
+    <t>警察 + 女人</t>
+  </si>
+  <si>
+    <t>n. 女警察；女警官</t>
+  </si>
+  <si>
+    <t>polite</t>
+  </si>
+  <si>
+    <t>坡上拿着梨的特警非常有礼貌。</t>
+  </si>
+  <si>
+    <t>adj. 有礼貌的；客气的；儒雅的；应酬的</t>
+  </si>
+  <si>
+    <t>pollute</t>
+  </si>
+  <si>
+    <t>斜坡的电线杆旁，骑着小鹿的特警在治理污染。</t>
+  </si>
+  <si>
+    <t>vt. 污染；弄脏</t>
+  </si>
+  <si>
+    <t>pocket</t>
+  </si>
+  <si>
+    <t>坡上的刺客从口袋里掏出一个ET外星人。</t>
+  </si>
+  <si>
+    <t>n. 衣袋，口袋；v. 把…放入口袋</t>
+  </si>
+  <si>
+    <t>power</t>
+  </si>
+  <si>
+    <t>坡上的女王发现尔康有很大的权力和能力。</t>
+  </si>
+  <si>
+    <t>n. 权力；能力；控制力；影响力；v. 驱动，推动；adj. 电力的</t>
+  </si>
+  <si>
+    <t>book</t>
+  </si>
+  <si>
+    <t>这本书有600篇课文，这不可能看完啊！</t>
+  </si>
+  <si>
+    <t>n. 书；印刷（或电子）出物；著作；v. 预约，预订</t>
+  </si>
+  <si>
+    <t>look</t>
+  </si>
+  <si>
+    <t>100篇课文，小威瞬间看完了。</t>
+  </si>
+  <si>
+    <t>v./n. 看；瞧；v. 寻找；int. 喂，听我说</t>
+  </si>
+  <si>
+    <t>cool</t>
+  </si>
+  <si>
+    <t>嫦娥用望远镜看光棍在凉爽的天气摆酷酷的姿势，棒极了。</t>
+  </si>
+  <si>
+    <t>adj. 凉爽的；凉快的；妙极的，酷的；v. （使）变凉，冷却；冷静下来；n. 凉气</t>
+  </si>
+  <si>
+    <t>pencil</t>
+  </si>
+  <si>
+    <t>盆里带刺的棍子被做成了铅笔。</t>
+  </si>
+  <si>
+    <t>n. 铅笔；石墨芯；化妆笔；v. 用铅笔写（或画、涂色）</t>
+  </si>
+  <si>
+    <t>animal</t>
+  </si>
+  <si>
+    <t>一摊泥里，妈妈用棍子救了一只小动物。</t>
+  </si>
+  <si>
+    <t>n. 动物；兽；牲畜</t>
+  </si>
+  <si>
+    <t>library</t>
+  </si>
+  <si>
+    <t>吃梨的病人，把一瓶乳液遗留在图书馆。</t>
+  </si>
+  <si>
+    <t>n. 图书馆；藏书楼</t>
+  </si>
+  <si>
+    <t>celebrate</t>
+  </si>
+  <si>
+    <t>厕所里，喝可乐的病人在庆祝球队夺冠。ate动词后缀</t>
+  </si>
+  <si>
+    <t>v. 庆祝；庆贺；赞美</t>
+  </si>
+  <si>
+    <t>celebration</t>
+  </si>
+  <si>
+    <t>celebrate去e + ion名词后缀</t>
+  </si>
+  <si>
+    <t>n. 庆祝；庆典；庆祝活动</t>
+  </si>
+  <si>
+    <t>kill</t>
+  </si>
+  <si>
+    <t>拿着机关枪的病人杀死一个敌人。</t>
+  </si>
+  <si>
+    <t>v./n. 杀死；v. 导致死亡；毁灭；破坏；扼杀；n. 捕杀；猎物</t>
+  </si>
+  <si>
+    <t>skill</t>
+  </si>
+  <si>
+    <t>白娘子杀了一个有很多技能的人。</t>
+  </si>
+  <si>
+    <t>n. 技能；技巧；技艺；技术；v. 有助于；有影响</t>
+  </si>
+  <si>
+    <t>skilled</t>
+  </si>
+  <si>
+    <t>skill + ed形容词后缀</t>
+  </si>
+  <si>
+    <t>adj. 熟练的；有技能的</t>
+  </si>
+  <si>
+    <t>brain</t>
+  </si>
+  <si>
+    <t>病人挨着门检查大脑。</t>
+  </si>
+  <si>
+    <t>n. 脑；智力；脑力</t>
+  </si>
+  <si>
+    <t>brave</t>
+  </si>
+  <si>
+    <t>病人吃了一颗维生素E后，变得很勇敢。</t>
+  </si>
+  <si>
+    <t>adj. 勇敢的；无畏的；vt. 勇敢面对；n. 勇敢的人</t>
+  </si>
+  <si>
+    <t>bring</t>
+  </si>
+  <si>
+    <t>病人把鹰带到医院来。</t>
+  </si>
+  <si>
+    <t>vt. 带来；带…到某处；取来；提供；导致</t>
+  </si>
+  <si>
+    <t>bridge</t>
+  </si>
+  <si>
+    <t>病人的ID身份证被哥哥在桥上捡到了。</t>
+  </si>
+  <si>
+    <t>n. 桥；纽带；vt. 在…建桥跨过；度过</t>
+  </si>
+  <si>
+    <t>out</t>
+  </si>
+  <si>
+    <t>偶像外出，在伞下晒太阳。</t>
+  </si>
+  <si>
+    <t>adv./prep. （从…里）出来；出去；外出</t>
+  </si>
+  <si>
+    <t>outdoor</t>
+  </si>
+  <si>
+    <t>外出 + 门</t>
+  </si>
+  <si>
+    <t>adj. 户外的；室外的</t>
+  </si>
+  <si>
+    <t>、</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3490,12 +3984,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D345"/>
+  <dimension ref="A1:D400"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="71.75" customWidth="1"/>
-    <col min="4" max="4" width="71.125" customWidth="1"/>
+    <col min="3" max="3" width="97.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.15">
@@ -4733,7 +5225,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A113" t="s">
         <v>335</v>
       </c>
@@ -4744,7 +5236,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A114" t="s">
         <v>338</v>
       </c>
@@ -4755,7 +5247,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A115" t="s">
         <v>341</v>
       </c>
@@ -4766,7 +5258,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A116" t="s">
         <v>344</v>
       </c>
@@ -4777,7 +5269,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A117" t="s">
         <v>347</v>
       </c>
@@ -4788,7 +5280,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A118" t="s">
         <v>350</v>
       </c>
@@ -4798,11 +5290,8 @@
       <c r="C118" t="s">
         <v>352</v>
       </c>
-      <c r="D118">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.15">
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A119" t="s">
         <v>353</v>
       </c>
@@ -4813,7 +5302,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A120" t="s">
         <v>356</v>
       </c>
@@ -4824,7 +5313,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A121" t="s">
         <v>359</v>
       </c>
@@ -4835,7 +5324,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A122" t="s">
         <v>362</v>
       </c>
@@ -4846,7 +5335,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A123" t="s">
         <v>365</v>
       </c>
@@ -4857,7 +5346,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A124" t="s">
         <v>368</v>
       </c>
@@ -4868,7 +5357,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A125" t="s">
         <v>371</v>
       </c>
@@ -4879,7 +5368,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A126" t="s">
         <v>374</v>
       </c>
@@ -4890,7 +5379,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A127" t="s">
         <v>377</v>
       </c>
@@ -4901,7 +5390,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A128" t="s">
         <v>380</v>
       </c>
@@ -5619,7 +6108,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A193" t="s">
         <v>575</v>
       </c>
@@ -5630,7 +6119,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A194" t="s">
         <v>578</v>
       </c>
@@ -5641,7 +6130,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A195" t="s">
         <v>581</v>
       </c>
@@ -5652,7 +6141,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A196" t="s">
         <v>584</v>
       </c>
@@ -5663,7 +6152,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A197" t="s">
         <v>587</v>
       </c>
@@ -5674,7 +6163,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A198" t="s">
         <v>590</v>
       </c>
@@ -5685,7 +6174,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A199" t="s">
         <v>593</v>
       </c>
@@ -5696,7 +6185,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A200" t="s">
         <v>596</v>
       </c>
@@ -5707,7 +6196,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A201" t="s">
         <v>599</v>
       </c>
@@ -5718,7 +6207,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A202" t="s">
         <v>602</v>
       </c>
@@ -5729,7 +6218,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A203" t="s">
         <v>605</v>
       </c>
@@ -5740,7 +6229,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A204" t="s">
         <v>608</v>
       </c>
@@ -5750,11 +6239,8 @@
       <c r="C204" t="s">
         <v>610</v>
       </c>
-      <c r="D204">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.15">
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A205" t="s">
         <v>611</v>
       </c>
@@ -5765,7 +6251,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A206" t="s">
         <v>614</v>
       </c>
@@ -5776,7 +6262,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A207" t="s">
         <v>617</v>
       </c>
@@ -5787,7 +6273,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A208" t="s">
         <v>620</v>
       </c>
@@ -6017,9 +6503,6 @@
       <c r="C228" t="s">
         <v>681</v>
       </c>
-      <c r="D228">
-        <v>1</v>
-      </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A229" t="s">
@@ -6042,9 +6525,6 @@
       <c r="C230" t="s">
         <v>687</v>
       </c>
-      <c r="D230">
-        <v>1</v>
-      </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A231" t="s">
@@ -6139,9 +6619,6 @@
       <c r="C238" t="s">
         <v>711</v>
       </c>
-      <c r="D238">
-        <v>1</v>
-      </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A239" t="s">
@@ -6153,9 +6630,6 @@
       <c r="C239" t="s">
         <v>714</v>
       </c>
-      <c r="D239">
-        <v>1</v>
-      </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A240" t="s">
@@ -6167,9 +6641,6 @@
       <c r="C240" t="s">
         <v>717</v>
       </c>
-      <c r="D240">
-        <v>1</v>
-      </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A241" t="s">
@@ -6228,9 +6699,6 @@
       <c r="C245" t="s">
         <v>732</v>
       </c>
-      <c r="D245">
-        <v>1</v>
-      </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A246" t="s">
@@ -6242,9 +6710,6 @@
       <c r="C246" t="s">
         <v>735</v>
       </c>
-      <c r="D246">
-        <v>1</v>
-      </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A247" t="s">
@@ -6259,138 +6724,126 @@
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A248" t="s">
-        <v>1031</v>
+        <v>739</v>
       </c>
       <c r="B248" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C248" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A249" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B249" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C249" t="s">
-        <v>743</v>
-      </c>
-      <c r="D249">
-        <v>1</v>
+        <v>744</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A250" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B250" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C250" t="s">
-        <v>746</v>
-      </c>
-      <c r="D250">
-        <v>1</v>
+        <v>747</v>
+      </c>
+      <c r="D250" t="s">
+        <v>1197</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A251" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B251" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C251" t="s">
-        <v>749</v>
-      </c>
-      <c r="D251">
-        <v>1</v>
+        <v>750</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A252" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B252" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C252" t="s">
-        <v>752</v>
-      </c>
-      <c r="D252">
-        <v>1</v>
+        <v>753</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A253" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B253" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C253" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A254" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B254" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C254" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A255" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B255" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C255" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A256" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B256" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C256" t="s">
-        <v>764</v>
-      </c>
-      <c r="D256">
-        <v>1</v>
+        <v>765</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A257" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B257" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C257" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A258" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B258" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C258" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D258">
         <v>1</v>
@@ -6398,13 +6851,13 @@
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A259" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B259" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C259" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="D259">
         <v>1</v>
@@ -6412,24 +6865,24 @@
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A260" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B260" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C260" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A261" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B261" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C261" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="D261">
         <v>1</v>
@@ -6437,46 +6890,46 @@
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A262" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B262" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C262" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A263" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B263" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C263" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A264" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B264" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C264" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A265" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B265" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C265" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D265">
         <v>1</v>
@@ -6484,254 +6937,233 @@
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A266" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B266" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C266" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A267" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B267" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C267" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A268" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B268" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C268" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A269" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B269" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C269" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A270" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B270" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C270" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A271" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B271" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C271" t="s">
-        <v>809</v>
-      </c>
-      <c r="D271">
-        <v>1</v>
+        <v>810</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A272" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B272" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C272" t="s">
-        <v>812</v>
-      </c>
-      <c r="D272">
-        <v>1</v>
+        <v>813</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A273" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B273" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C273" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A274" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B274" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C274" t="s">
-        <v>818</v>
-      </c>
-      <c r="D274">
-        <v>1</v>
+        <v>819</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A275" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B275" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C275" t="s">
-        <v>821</v>
-      </c>
-      <c r="D275">
-        <v>1</v>
+        <v>822</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A276" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B276" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C276" t="s">
-        <v>824</v>
-      </c>
-      <c r="D276">
-        <v>1</v>
+        <v>825</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A277" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B277" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C277" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A278" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B278" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C278" t="s">
-        <v>830</v>
-      </c>
-      <c r="D278">
-        <v>1</v>
+        <v>831</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A279" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B279" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C279" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A280" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B280" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C280" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A281" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B281" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C281" t="s">
-        <v>839</v>
-      </c>
-      <c r="D281">
-        <v>1</v>
+        <v>840</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A282" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B282" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C282" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A283" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B283" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C283" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A284" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B284" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C284" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A285" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B285" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C285" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A286" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B286" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C286" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="D286">
         <v>1</v>
@@ -6739,13 +7171,13 @@
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A287" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B287" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C287" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="D287">
         <v>1</v>
@@ -6753,13 +7185,13 @@
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A288" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B288" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C288" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="D288">
         <v>1</v>
@@ -6767,13 +7199,13 @@
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A289" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B289" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C289" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D289">
         <v>1</v>
@@ -6781,52 +7213,46 @@
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A290" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B290" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C290" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A291" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B291" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C291" t="s">
-        <v>869</v>
-      </c>
-      <c r="D291">
-        <v>1</v>
+        <v>870</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A292" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B292" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C292" t="s">
-        <v>872</v>
-      </c>
-      <c r="D292">
-        <v>1</v>
+        <v>873</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A293" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B293" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C293" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D293">
         <v>1</v>
@@ -6834,88 +7260,79 @@
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A294" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B294" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C294" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A295" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B295" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C295" t="s">
-        <v>881</v>
-      </c>
-      <c r="D295">
-        <v>1</v>
+        <v>882</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A296" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B296" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C296" t="s">
-        <v>884</v>
-      </c>
-      <c r="D296">
-        <v>1</v>
+        <v>885</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A297" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B297" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C297" t="s">
-        <v>887</v>
-      </c>
-      <c r="D297">
-        <v>1</v>
+        <v>888</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A298" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B298" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C298" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A299" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B299" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C299" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A300" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B300" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C300" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="D300">
         <v>1</v>
@@ -6923,66 +7340,57 @@
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A301" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B301" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C301" t="s">
-        <v>899</v>
-      </c>
-      <c r="D301">
-        <v>1</v>
+        <v>900</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A302" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B302" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C302" t="s">
-        <v>902</v>
-      </c>
-      <c r="D302">
-        <v>1</v>
+        <v>903</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A303" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B303" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C303" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A304" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B304" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C304" t="s">
-        <v>908</v>
-      </c>
-      <c r="D304">
-        <v>1</v>
+        <v>909</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A305" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B305" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C305" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="D305">
         <v>1</v>
@@ -6990,60 +7398,57 @@
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A306" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B306" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="C306" t="s">
-        <v>914</v>
-      </c>
-      <c r="D306">
-        <v>1</v>
+        <v>915</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A307" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B307" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C307" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A308" t="s">
-        <v>1032</v>
+        <v>919</v>
       </c>
       <c r="B308" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="C308" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A309" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B309" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="C309" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A310" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="B310" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="C310" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="D310">
         <v>1</v>
@@ -7051,27 +7456,24 @@
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A311" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="B311" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="C311" t="s">
-        <v>928</v>
-      </c>
-      <c r="D311">
-        <v>1</v>
+        <v>930</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A312" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="B312" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="C312" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="D312">
         <v>1</v>
@@ -7079,13 +7481,13 @@
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A313" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="B313" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="C313" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="D313">
         <v>1</v>
@@ -7093,27 +7495,24 @@
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A314" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="B314" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="C314" t="s">
-        <v>937</v>
-      </c>
-      <c r="D314">
-        <v>1</v>
+        <v>939</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A315" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="B315" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="C315" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="D315">
         <v>1</v>
@@ -7121,13 +7520,13 @@
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A316" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="B316" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="C316" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="D316">
         <v>1</v>
@@ -7135,91 +7534,79 @@
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A317" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="B317" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="C317" t="s">
-        <v>946</v>
-      </c>
-      <c r="D317">
-        <v>1</v>
+        <v>948</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A318" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="B318" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="C318" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A319" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="B319" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="C319" t="s">
-        <v>952</v>
-      </c>
-      <c r="D319">
-        <v>1</v>
+        <v>954</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A320" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="B320" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="C320" t="s">
-        <v>955</v>
-      </c>
-      <c r="D320">
-        <v>1</v>
+        <v>957</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A321" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="B321" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="C321" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A322" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="B322" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="C322" t="s">
-        <v>961</v>
-      </c>
-      <c r="D322">
-        <v>1</v>
+        <v>963</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A323" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="B323" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="C323" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="D323">
         <v>1</v>
@@ -7227,24 +7614,24 @@
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A324" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="B324" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="C324" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A325" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="B325" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="C325" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="D325">
         <v>1</v>
@@ -7252,55 +7639,46 @@
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A326" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="B326" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="C326" t="s">
-        <v>973</v>
-      </c>
-      <c r="D326">
-        <v>1</v>
+        <v>975</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A327" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="B327" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="C327" t="s">
-        <v>976</v>
-      </c>
-      <c r="D327">
-        <v>1</v>
+        <v>978</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A328" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="B328" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="C328" t="s">
-        <v>979</v>
-      </c>
-      <c r="D328">
-        <v>1</v>
+        <v>981</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A329" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="B329" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="C329" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="D329">
         <v>1</v>
@@ -7308,13 +7686,13 @@
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A330" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="B330" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="C330" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="D330">
         <v>1</v>
@@ -7322,41 +7700,35 @@
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A331" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="B331" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="C331" t="s">
-        <v>988</v>
-      </c>
-      <c r="D331">
-        <v>1</v>
+        <v>990</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A332" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="B332" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="C332" t="s">
-        <v>991</v>
-      </c>
-      <c r="D332">
-        <v>1</v>
+        <v>993</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A333" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="B333" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="C333" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="D333">
         <v>1</v>
@@ -7364,13 +7736,13 @@
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A334" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="B334" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="C334" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="D334">
         <v>1</v>
@@ -7378,35 +7750,35 @@
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A335" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="B335" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="C335" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A336" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="B336" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="C336" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A337" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="B337" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="C337" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="D337">
         <v>1</v>
@@ -7414,13 +7786,13 @@
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A338" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="B338" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="C338" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="D338">
         <v>1</v>
@@ -7428,97 +7800,807 @@
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A339" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="B339" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="C339" t="s">
-        <v>1012</v>
-      </c>
-      <c r="D339">
-        <v>1</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A340" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="B340" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="C340" t="s">
-        <v>1015</v>
-      </c>
-      <c r="D340">
-        <v>1</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A341" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="B341" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="C341" t="s">
-        <v>1018</v>
-      </c>
-      <c r="D341">
-        <v>1</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A342" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="B342" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="C342" t="s">
-        <v>1021</v>
-      </c>
-      <c r="D342">
-        <v>1</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A343" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="B343" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="C343" t="s">
-        <v>1024</v>
-      </c>
-      <c r="D343">
-        <v>1</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A344" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="B344" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="C344" t="s">
-        <v>1027</v>
-      </c>
-      <c r="D344">
-        <v>1</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A345" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="B345" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="C345" t="s">
-        <v>1030</v>
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A346" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B346" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C346" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D346">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A347" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B347" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C347" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D347">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A348" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B348" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C348" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D348">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A349" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B349" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C349" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D349">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A350" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B350" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C350" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D350">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A351" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B351" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C351" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D351">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A352" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B352" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C352" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D352">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A353" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B353" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C353" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D353">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A354" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B354" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C354" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D354">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A355" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B355" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C355" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A356" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B356" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C356" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D356">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A357" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B357" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C357" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D357">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A358" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B358" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C358" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D358">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A359" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B359" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C359" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D359">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A360" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B360" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C360" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D360">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A361" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B361" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C361" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D361">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A362" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B362" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C362" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D362">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A363" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B363" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C363" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D363">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A364" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B364" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C364" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D364">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A365" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B365" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C365" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D365">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A366" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B366" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C366" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D366">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A367" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B367" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C367" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A368" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B368" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C368" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D368">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A369" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B369" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C369" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A370" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B370" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C370" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A371" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B371" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C371" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A372" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C372" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A373" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B373" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C373" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D373">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A374" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B374" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C374" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D374">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A375" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B375" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C375" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D375">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A376" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B376" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C376" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D376">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A377" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B377" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C377" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A378" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B378" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C378" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A379" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B379" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C379" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A380" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B380" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C380" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D380">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A381" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B381" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C381" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D381">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A382" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B382" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C382" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D382">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A383" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B383" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C383" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A384" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B384" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C384" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A385" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B385" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C385" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A386" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B386" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C386" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D386">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A387" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B387" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C387" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D387">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A388" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B388" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C388" t="s">
+        <v>1160</v>
+      </c>
+      <c r="D388">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A389" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B389" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C389" t="s">
+        <v>1163</v>
+      </c>
+      <c r="D389">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A390" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B390" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C390" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D390">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A391" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B391" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C391" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D391">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A392" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B392" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C392" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A393" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B393" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C393" t="s">
+        <v>1175</v>
+      </c>
+      <c r="D393">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A394" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B394" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C394" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D394">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A395" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B395" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C395" t="s">
+        <v>1181</v>
+      </c>
+      <c r="D395">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A396" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B396" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C396" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D396">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A397" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B397" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C397" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D397">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A398" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B398" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C398" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D398">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A399" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B399" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C399" t="s">
+        <v>1193</v>
+      </c>
+      <c r="D399">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A400" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B400" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C400" t="s">
+        <v>1196</v>
+      </c>
+      <c r="D400">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Single_word.xlsx
+++ b/Single_word.xlsx
@@ -6632,7 +6632,9 @@
           <t>position</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr"/>
+      <c r="B259" t="n">
+        <v>1</v>
+      </c>
       <c r="C259" t="inlineStr">
         <is>
           <t>po·si·tion</t>
@@ -9527,7 +9529,9 @@
           <t>policeman</t>
         </is>
       </c>
-      <c r="B378" t="inlineStr"/>
+      <c r="B378" t="n">
+        <v>1</v>
+      </c>
       <c r="C378" t="inlineStr">
         <is>
           <t>po·lice·man</t>
@@ -10436,7 +10440,9 @@
           <t>wish</t>
         </is>
       </c>
-      <c r="B409" t="inlineStr"/>
+      <c r="B409" t="n">
+        <v>1</v>
+      </c>
       <c r="C409" t="inlineStr">
         <is>
           <t>wish</t>
@@ -15228,7 +15234,9 @@
           <t>strict</t>
         </is>
       </c>
-      <c r="B573" t="inlineStr"/>
+      <c r="B573" t="n">
+        <v>1</v>
+      </c>
       <c r="C573" t="inlineStr">
         <is>
           <t>strict</t>
